--- a/trackDB/seasonOverview.xlsx
+++ b/trackDB/seasonOverview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lholliday/SimEnv/trackDB/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SimEnv\trackDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10D76EF-F358-C740-84F6-DF7F26DB65C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E48C323-A5F8-4EAE-B74F-0CFC05DFD592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Track</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>WIN</t>
+  </si>
+  <si>
+    <t>LapDistance </t>
+  </si>
+  <si>
+    <t>CentreLineDistance</t>
   </si>
 </sst>
 </file>
@@ -148,6 +154,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>42649</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>35541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>406533</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>139709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F042525-FF08-9211-1F05-F121BC1B591C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6496903" y="3490131"/>
+          <a:ext cx="2723809" cy="1447619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,10 +468,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,8 +492,14 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -449,8 +515,14 @@
       <c r="E2">
         <v>280</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>3000</v>
+      </c>
+      <c r="G2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -466,8 +538,14 @@
       <c r="E3">
         <v>290</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>3000</v>
+      </c>
+      <c r="G3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -483,8 +561,14 @@
       <c r="E4">
         <v>270</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>3000</v>
+      </c>
+      <c r="G4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -500,8 +584,14 @@
       <c r="E5">
         <v>265</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>3000</v>
+      </c>
+      <c r="G5">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -517,8 +607,14 @@
       <c r="E6">
         <v>280</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>3000</v>
+      </c>
+      <c r="G6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -534,8 +630,14 @@
       <c r="E7">
         <v>280</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>3000</v>
+      </c>
+      <c r="G7">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -551,8 +653,14 @@
       <c r="E8">
         <v>280</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>3000</v>
+      </c>
+      <c r="G8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -568,8 +676,14 @@
       <c r="E9">
         <v>280</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>3000</v>
+      </c>
+      <c r="G9">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -585,8 +699,14 @@
       <c r="E10">
         <v>400</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>3000</v>
+      </c>
+      <c r="G10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -602,8 +722,14 @@
       <c r="E11">
         <v>280</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>3360</v>
+      </c>
+      <c r="G11">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -619,8 +745,14 @@
       <c r="E12">
         <v>280</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>6172</v>
+      </c>
+      <c r="G12">
+        <v>6213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -636,8 +768,14 @@
       <c r="E13">
         <v>280</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>3000</v>
+      </c>
+      <c r="G13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -653,8 +791,14 @@
       <c r="E14">
         <v>280</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>3000</v>
+      </c>
+      <c r="G14">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -670,8 +814,14 @@
       <c r="E15">
         <v>280</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>3000</v>
+      </c>
+      <c r="G15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -687,8 +837,15 @@
       <c r="E16">
         <v>280</v>
       </c>
+      <c r="F16">
+        <v>3000</v>
+      </c>
+      <c r="G16">
+        <v>3000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>